--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_44.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3762670.894734366</v>
+        <v>3799028.941041582</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370116962595</v>
+        <v>603.5370117098098</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370116962595</v>
+        <v>603.5370117098098</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>85.50414770182039</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>52.77315824183916</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>120.2009292895605</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -912,7 +912,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>85.50414770182039</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>288.5193398012008</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X6" t="n">
-        <v>173.5614789353153</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1261,10 +1261,10 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>326.4539748586856</v>
+        <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>119.3122985375318</v>
       </c>
       <c r="V9" t="n">
         <v>374</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>158.5198244189524</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
@@ -1453,16 +1453,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,28 +1489,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
-        <v>81.3753501231742</v>
+        <v>254.9671660051473</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,16 +1565,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243966</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G14" t="n">
         <v>81.3744577141519</v>
@@ -1623,7 +1623,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>18.63624233787687</v>
@@ -1702,7 +1702,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>173.591815881973</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1735,19 +1735,19 @@
         <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U15" t="n">
         <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>78.39139276613435</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,7 +1802,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
@@ -1851,7 +1851,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G17" t="n">
         <v>81.3744577141519</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>213.6917283274924</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1936,10 +1936,10 @@
         <v>3.99961134672543</v>
       </c>
       <c r="H18" t="n">
-        <v>4.021973978873973</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1963,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
-        <v>501.333570877285</v>
+        <v>404.6459244566755</v>
       </c>
       <c r="S18" t="n">
         <v>131.8202263797057</v>
@@ -2039,7 +2039,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P19" t="n">
-        <v>290.5838154131063</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q19" t="n">
         <v>352.895266425598</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G20" t="n">
         <v>81.3744577141519</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2158,22 +2158,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>177.6137898608469</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V21" t="n">
         <v>93.51066719152016</v>
@@ -2224,7 +2224,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2285,7 +2285,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090244326</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>83.88962870801186</v>
+        <v>84.350216073326</v>
       </c>
       <c r="G23" t="n">
         <v>81.37445771415189</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2395,16 +2395,16 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.999611346725456</v>
@@ -2449,19 +2449,19 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>251.9832086481075</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2522,7 +2522,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>192.2280582198499</v>
       </c>
       <c r="G27" t="n">
         <v>3.999611346725456</v>
@@ -2674,31 +2674,31 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>226.7834941523314</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
         <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M28" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N28" t="n">
         <v>155.2579933044718</v>
@@ -2808,7 +2808,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2853,7 +2853,7 @@
         <v>317.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>271.2818334606677</v>
+        <v>271.7424208259818</v>
       </c>
       <c r="Y29" t="n">
         <v>190.3174326828064</v>
@@ -2872,13 +2872,13 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>3.999611346725456</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>180.333570877285</v>
@@ -2926,16 +2926,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
-        <v>188.4739349641461</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>251.9832086481075</v>
       </c>
     </row>
     <row r="31">
@@ -3036,7 +3036,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G32" t="n">
         <v>81.3744577141519</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3106,7 +3106,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3121,7 +3121,7 @@
         <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>98.98524175149979</v>
+        <v>177.6137898608468</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>180.333570877285</v>
@@ -3166,7 +3166,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3218,7 +3218,7 @@
         <v>102.3923982877958</v>
       </c>
       <c r="N34" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O34" t="n">
         <v>231.765039488851</v>
@@ -3233,7 +3233,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
@@ -3349,16 +3349,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608469</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3385,22 +3385,22 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>226.7834941523317</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>111.3731429098285</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090246937</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3580,7 +3580,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>26.93768689770263</v>
@@ -3592,13 +3592,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490371</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,10 +3643,10 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>323.1750930247779</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090247613</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949504</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3823,19 +3823,19 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>195.2639131038861</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H42" t="n">
         <v>325.021973978874</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,19 +3859,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>501.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>356.1325799590961</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
         <v>93.51066719152016</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090251439</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,28 +4051,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
-        <v>94.9632677726258</v>
+        <v>173.5918158819728</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090252531</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
@@ -4324,19 +4324,19 @@
         <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M2" t="n">
-        <v>834.5019149748744</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
         <v>1125.74</v>
@@ -4345,28 +4345,28 @@
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>929.6586976417566</v>
+        <v>731.2643675825382</v>
       </c>
       <c r="C3" t="n">
-        <v>929.6586976417566</v>
+        <v>366.5169812739328</v>
       </c>
       <c r="D3" t="n">
-        <v>578.2064886541781</v>
+        <v>366.5169812739328</v>
       </c>
       <c r="E3" t="n">
-        <v>578.2064886541781</v>
+        <v>366.5169812739328</v>
       </c>
       <c r="F3" t="n">
-        <v>578.2064886541781</v>
+        <v>366.5169812739328</v>
       </c>
       <c r="G3" t="n">
-        <v>578.2064886541781</v>
+        <v>366.5169812739328</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1442.693779553698</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1064.91600177592</v>
+        <v>1360.997993968056</v>
       </c>
       <c r="S3" t="n">
-        <v>1001.79599037656</v>
+        <v>1297.877982568697</v>
       </c>
       <c r="T3" t="n">
-        <v>997.2773596060584</v>
+        <v>920.1002047909187</v>
       </c>
       <c r="U3" t="n">
-        <v>997.079454759672</v>
+        <v>798.6851247004536</v>
       </c>
       <c r="V3" t="n">
-        <v>982.4222151722779</v>
+        <v>784.0278851130595</v>
       </c>
       <c r="W3" t="n">
-        <v>949.7220708189158</v>
+        <v>751.3277407596973</v>
       </c>
       <c r="X3" t="n">
-        <v>929.6586976417566</v>
+        <v>731.2643675825382</v>
       </c>
       <c r="Y3" t="n">
-        <v>929.6586976417566</v>
+        <v>731.2643675825382</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253.0866383453244</v>
+        <v>29.92</v>
       </c>
       <c r="C4" t="n">
-        <v>379.0886441637601</v>
+        <v>109.6413159146684</v>
       </c>
       <c r="D4" t="n">
-        <v>492.4077882887602</v>
+        <v>222.9604600396685</v>
       </c>
       <c r="E4" t="n">
-        <v>610.2366925001733</v>
+        <v>340.7893642510815</v>
       </c>
       <c r="F4" t="n">
-        <v>734.5976650921087</v>
+        <v>465.150336843017</v>
       </c>
       <c r="G4" t="n">
-        <v>888.1863260609612</v>
+        <v>618.7389978118695</v>
       </c>
       <c r="H4" t="n">
-        <v>1059.321902040031</v>
+        <v>789.8745737909392</v>
       </c>
       <c r="I4" t="n">
-        <v>1285.930876713819</v>
+        <v>1016.483548464727</v>
       </c>
       <c r="J4" t="n">
         <v>1386.743548464727</v>
@@ -4524,7 +4524,7 @@
         <v>29.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>141.3293006790323</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>211.4278628071088</v>
       </c>
       <c r="K5" t="n">
-        <v>770.4399999999999</v>
+        <v>263.0661931588676</v>
       </c>
       <c r="L5" t="n">
-        <v>834.5019149748742</v>
+        <v>327.128108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>1204.761914974874</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="6">
@@ -4658,25 +4658,25 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>968.469334165078</v>
+        <v>1201.352353801666</v>
       </c>
       <c r="S6" t="n">
-        <v>590.6915563873001</v>
+        <v>1138.232342402307</v>
       </c>
       <c r="T6" t="n">
-        <v>586.1729256167982</v>
+        <v>1133.713711631805</v>
       </c>
       <c r="U6" t="n">
-        <v>585.9750207704118</v>
+        <v>1133.515806785418</v>
       </c>
       <c r="V6" t="n">
-        <v>571.3177811830177</v>
+        <v>1118.858567198024</v>
       </c>
       <c r="W6" t="n">
-        <v>538.6176368296556</v>
+        <v>741.0807894202462</v>
       </c>
       <c r="X6" t="n">
         <v>363.3030116424684</v>
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="C7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="D7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="E7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>940.0895325918727</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1310.349532591873</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4752,16 +4752,16 @@
         <v>505.7585226289696</v>
       </c>
       <c r="V7" t="n">
-        <v>700.1293446184156</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="W7" t="n">
-        <v>700.1293446184156</v>
+        <v>677.649440888647</v>
       </c>
       <c r="X7" t="n">
-        <v>700.1293446184156</v>
+        <v>828.6802319128404</v>
       </c>
       <c r="Y7" t="n">
-        <v>700.1293446184156</v>
+        <v>940.0895325918727</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4801,19 +4801,19 @@
         <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>515.8802453266331</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M8" t="n">
-        <v>886.1402453266331</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="N8" t="n">
-        <v>1256.400245326633</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="O8" t="n">
-        <v>1256.400245326633</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="P8" t="n">
-        <v>1314.492137192891</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>818.3736047553042</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>818.1756999089177</v>
+        <v>1169.627908896496</v>
       </c>
       <c r="V9" t="n">
-        <v>440.39792213114</v>
+        <v>791.8501311187184</v>
       </c>
       <c r="W9" t="n">
-        <v>407.6977777777778</v>
+        <v>759.1499867653563</v>
       </c>
       <c r="X9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>774.8297405151413</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="C10" t="n">
-        <v>900.8317463335771</v>
+        <v>344.620323690067</v>
       </c>
       <c r="D10" t="n">
-        <v>1014.150890458577</v>
+        <v>457.9394678150671</v>
       </c>
       <c r="E10" t="n">
-        <v>1131.97979466999</v>
+        <v>575.7683720264802</v>
       </c>
       <c r="F10" t="n">
-        <v>1256.340767261926</v>
+        <v>700.1293446184156</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>853.7180055872682</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1024.853581566338</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="V10" t="n">
-        <v>228.741392885946</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="W10" t="n">
-        <v>400.6323111456234</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="X10" t="n">
-        <v>551.6631021698169</v>
+        <v>218.6183178716313</v>
       </c>
       <c r="Y10" t="n">
-        <v>663.0724028488492</v>
+        <v>218.6183178716313</v>
       </c>
     </row>
     <row r="11">
@@ -5008,49 +5008,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>733.5813277110226</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L11" t="n">
-        <v>1376.091327711023</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M11" t="n">
-        <v>1651.83297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
         <v>2596</v>
@@ -5068,16 +5068,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5093,16 +5093,16 @@
         <v>776.43273917484</v>
       </c>
       <c r="D12" t="n">
-        <v>424.9805301872615</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E12" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R12" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S12" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T12" t="n">
-        <v>1767.260375227614</v>
+        <v>1671.337882527992</v>
       </c>
       <c r="U12" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V12" t="n">
-        <v>1592.843862392842</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W12" t="n">
-        <v>1480.3457382415</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X12" t="n">
-        <v>1056.241961023937</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y12" t="n">
-        <v>977.0587360076396</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="13">
@@ -5190,31 +5190,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J13" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611868</v>
       </c>
       <c r="K13" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.080700024147</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405757</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.22798246859</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605487</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111698</v>
       </c>
       <c r="P13" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645225</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881608</v>
       </c>
       <c r="R13" t="n">
-        <v>82.79157247680381</v>
+        <v>81.9448594974138</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5257,13 +5257,13 @@
         <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G14" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H14" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
@@ -5272,22 +5272,22 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>733.5813277110226</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L14" t="n">
-        <v>1205.91497964478</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M14" t="n">
-        <v>1205.91497964478</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N14" t="n">
-        <v>1205.91497964478</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O14" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P14" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>343.7981213238219</v>
+        <v>668.0405455662462</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>627.5355835000652</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>600.325798754911</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176255</v>
       </c>
       <c r="F15" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463101</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>227.2652685676495</v>
       </c>
       <c r="I15" t="n">
         <v>51.92</v>
@@ -5378,16 +5378,16 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V15" t="n">
         <v>1348.024214018445</v>
       </c>
       <c r="W15" t="n">
-        <v>911.2836656246791</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X15" t="n">
         <v>811.4223126495401</v>
@@ -5433,16 +5433,16 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M16" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N16" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O16" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P16" t="n">
         <v>820.7766206439126</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C17" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D17" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E17" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F17" t="n">
         <v>207.6991338872047</v>
@@ -5506,13 +5506,13 @@
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>775.9368380887173</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L17" t="n">
-        <v>1009.32297330616</v>
+        <v>1417.990475851726</v>
       </c>
       <c r="M17" t="n">
         <v>1651.83297330616</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X17" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1019.853205197711</v>
+        <v>1010.52448325439</v>
       </c>
       <c r="C18" t="n">
-        <v>804.0029745638803</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D18" t="n">
-        <v>452.5507655763019</v>
+        <v>618.5673122006306</v>
       </c>
       <c r="E18" t="n">
-        <v>430.6597582814406</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F18" t="n">
-        <v>411.835271071464</v>
+        <v>577.8518176957928</v>
       </c>
       <c r="G18" t="n">
-        <v>407.7952596101252</v>
+        <v>573.8118062344539</v>
       </c>
       <c r="H18" t="n">
-        <v>403.7326596314647</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I18" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="J18" t="n">
-        <v>596.8967549011032</v>
+        <v>245.0840952696386</v>
       </c>
       <c r="K18" t="n">
-        <v>904.3763400520904</v>
+        <v>552.5636804206258</v>
       </c>
       <c r="L18" t="n">
-        <v>1334.777960137857</v>
+        <v>982.9653005063919</v>
       </c>
       <c r="M18" t="n">
-        <v>1606.463701880716</v>
+        <v>1254.651042249251</v>
       </c>
       <c r="N18" t="n">
-        <v>1930.261603846775</v>
+        <v>1578.44894421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2343.590454775776</v>
+        <v>1991.777795144312</v>
       </c>
       <c r="P18" t="n">
-        <v>2596</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2596</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>2089.602453659308</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S18" t="n">
-        <v>1956.450709841424</v>
+        <v>1622.879563655678</v>
       </c>
       <c r="T18" t="n">
-        <v>1874.253386484682</v>
+        <v>1540.682240298936</v>
       </c>
       <c r="U18" t="n">
-        <v>1794.292093035284</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V18" t="n">
-        <v>1699.83687364991</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W18" t="n">
-        <v>1587.338749498568</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X18" t="n">
-        <v>1487.477396523429</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y18" t="n">
-        <v>1408.294171507132</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="19">
@@ -5682,13 +5682,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q19" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R19" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C20" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D20" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E20" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F20" t="n">
         <v>207.6991338872047</v>
@@ -5743,52 +5743,52 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>307.5796384907274</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L20" t="n">
-        <v>950.0896384907273</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.599638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>2235.109638490728</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>2396.239739873683</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2592.831746212303</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>668.0405455662462</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C21" t="n">
-        <v>627.5355835000652</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D21" t="n">
-        <v>600.325798754911</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E21" t="n">
-        <v>254.1923672176255</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F21" t="n">
-        <v>235.3678800076489</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G21" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5855,19 +5855,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U21" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1235.526089867103</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>1135.664736891964</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>732.2390876332428</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6440969023969</v>
+        <v>686.6440969024017</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4361027208327</v>
+        <v>734.4361027208374</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5452468458327</v>
+        <v>769.5452468458375</v>
       </c>
       <c r="E22" t="n">
-        <v>809.1641510572457</v>
+        <v>809.1641510572505</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3151236491811</v>
+        <v>855.3151236491859</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1258141262304</v>
+        <v>931.1258141262351</v>
       </c>
       <c r="H22" t="n">
-        <v>1027.892525187267</v>
+        <v>1027.892525187272</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.283805434826</v>
+        <v>1189.28380543483</v>
       </c>
       <c r="J22" t="n">
-        <v>1515.576154611867</v>
+        <v>1515.576154611872</v>
       </c>
       <c r="K22" t="n">
-        <v>1619.080700024145</v>
+        <v>1619.08070002415</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405756</v>
+        <v>1608.654647405761</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468588</v>
+        <v>1505.227982468593</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1348.401726605491</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1114.295626111702</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645261</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881645</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741744</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4096660440508</v>
+        <v>164.4096660440556</v>
       </c>
       <c r="U22" t="n">
-        <v>332.7843563872555</v>
+        <v>332.7843563872602</v>
       </c>
       <c r="V22" t="n">
-        <v>453.3957492732014</v>
+        <v>453.3957492732062</v>
       </c>
       <c r="W22" t="n">
-        <v>547.0766675328789</v>
+        <v>547.0766675328837</v>
       </c>
       <c r="X22" t="n">
-        <v>619.8974585570725</v>
+        <v>619.8974585570772</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.0967592361047</v>
+        <v>653.0967592361095</v>
       </c>
     </row>
     <row r="23">
@@ -5956,16 +5956,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D23" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E23" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F23" t="n">
         <v>207.6991338872046</v>
@@ -5980,52 +5980,52 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L23" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1634.498786631431</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N23" t="n">
-        <v>1651.83297330616</v>
+        <v>2234.653276253736</v>
       </c>
       <c r="O23" t="n">
-        <v>1812.963074689115</v>
+        <v>2395.783377636692</v>
       </c>
       <c r="P23" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.375383975311</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
         <v>60.02261143999941</v>
@@ -6092,19 +6092,19 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>911.2836656246793</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>487.1798884071161</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.6513948231691</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L25" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M25" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N25" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O25" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6217,13 +6217,13 @@
         <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>133.4268380887174</v>
+        <v>310.7478922784252</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>953.2578922784252</v>
       </c>
       <c r="L26" t="n">
-        <v>991.9887866314309</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="M26" t="n">
         <v>1595.767892278425</v>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>492.6952769985969</v>
+        <v>343.7981213238222</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1903149324158</v>
+        <v>303.293159257641</v>
       </c>
       <c r="D27" t="n">
-        <v>424.9805301872616</v>
+        <v>276.0833745124868</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176256</v>
       </c>
       <c r="F27" t="n">
         <v>60.02261143999941</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1753.535205884734</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1347.095458285568</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>1267.13416483617</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V27" t="n">
-        <v>1172.678945450796</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W27" t="n">
-        <v>735.9383970570298</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X27" t="n">
-        <v>636.0770440818908</v>
+        <v>811.4223126495403</v>
       </c>
       <c r="Y27" t="n">
-        <v>556.8938190655934</v>
+        <v>407.9966633908188</v>
       </c>
     </row>
     <row r="28">
@@ -6381,7 +6381,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M28" t="n">
         <v>1506.07469544798</v>
@@ -6430,43 +6430,43 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C29" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D29" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E29" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F29" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G29" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H29" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I29" t="n">
         <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L29" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M29" t="n">
-        <v>1166.141587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N29" t="n">
-        <v>1170.453074689115</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O29" t="n">
         <v>1812.963074689115</v>
@@ -6496,10 +6496,10 @@
         <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.937701241021</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C30" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872616</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
         <v>60.02261143999941</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R30" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.92136969322</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W30" t="n">
-        <v>1060.180821299454</v>
+        <v>911.2836656246793</v>
       </c>
       <c r="X30" t="n">
-        <v>960.3194683243149</v>
+        <v>487.1798884071161</v>
       </c>
       <c r="Y30" t="n">
-        <v>881.1362433080176</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="31">
@@ -6667,16 +6667,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
         <v>207.6991338872047</v>
@@ -6697,46 +6697,46 @@
         <v>1201.938527309012</v>
       </c>
       <c r="L32" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M32" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N32" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>2005.578628691967</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
-        <v>2202.170635030587</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>912.8601939406431</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>872.355231874462</v>
+        <v>951.7780077424893</v>
       </c>
       <c r="D33" t="n">
-        <v>845.1454471293079</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E33" t="n">
-        <v>499.0120155920224</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F33" t="n">
-        <v>155.9451041396214</v>
+        <v>235.3678800076487</v>
       </c>
       <c r="G33" t="n">
-        <v>151.9050926782826</v>
+        <v>231.3278685463099</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R33" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S33" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T33" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U33" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V33" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1156.103313999076</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1056.241961023937</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>977.0587360076396</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="34">
@@ -6861,19 +6861,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6916,7 +6916,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G35" t="n">
         <v>125.5027119537179</v>
@@ -6931,22 +6931,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L35" t="n">
-        <v>1418.446838088717</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M35" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N35" t="n">
-        <v>1651.83297330616</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O35" t="n">
-        <v>1812.963074689115</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P35" t="n">
-        <v>2009.555081027735</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q35" t="n">
         <v>2596</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>816.937701241021</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C36" t="n">
-        <v>776.43273917484</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D36" t="n">
-        <v>424.9805301872616</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E36" t="n">
-        <v>403.0895228924003</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463101</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1753.535205884733</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1671.337882527992</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>960.3194683243149</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>881.1362433080176</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7062,55 +7062,55 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>686.644096902428</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C37" t="n">
-        <v>734.4361027208638</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D37" t="n">
-        <v>769.5452468458639</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E37" t="n">
-        <v>809.1641510572769</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F37" t="n">
-        <v>855.3151236492123</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G37" t="n">
-        <v>931.1258141262615</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H37" t="n">
-        <v>1027.892525187298</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I37" t="n">
-        <v>1189.283805434857</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J37" t="n">
-        <v>1515.576154611898</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K37" t="n">
-        <v>1619.080700024177</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L37" t="n">
-        <v>1608.654647405787</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M37" t="n">
-        <v>1505.22798246862</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N37" t="n">
-        <v>1348.401726605517</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O37" t="n">
-        <v>1114.295626111728</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645525</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881908</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949744382</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7128,10 +7128,10 @@
         <v>547.0766675328789</v>
       </c>
       <c r="X37" t="n">
-        <v>619.8974585571036</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y37" t="n">
-        <v>653.0967592361359</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="38">
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7171,10 +7171,10 @@
         <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>949.6332762537361</v>
+        <v>1376.091327711023</v>
       </c>
       <c r="M38" t="n">
-        <v>1009.32297330616</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N38" t="n">
         <v>1651.83297330616</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>686.2820590119659</v>
+        <v>492.6952769985969</v>
       </c>
       <c r="C39" t="n">
-        <v>321.5346727033605</v>
+        <v>452.1903149324157</v>
       </c>
       <c r="D39" t="n">
-        <v>294.3248879582063</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E39" t="n">
-        <v>272.4338806633451</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>253.6093934533685</v>
+        <v>384.2650356824237</v>
       </c>
       <c r="G39" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R39" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S39" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1687.299081778216</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V39" t="n">
-        <v>1592.843862392842</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W39" t="n">
-        <v>1156.103313999076</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X39" t="n">
-        <v>829.6638260952598</v>
+        <v>960.319468324315</v>
       </c>
       <c r="Y39" t="n">
-        <v>750.4806010789624</v>
+        <v>556.8938190655934</v>
       </c>
     </row>
     <row r="40">
@@ -7323,31 +7323,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J40" t="n">
-        <v>1515.576154611905</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K40" t="n">
-        <v>1619.080700024184</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L40" t="n">
-        <v>1608.654647405794</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M40" t="n">
-        <v>1505.227982468627</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N40" t="n">
-        <v>1348.401726605524</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O40" t="n">
-        <v>1114.295626111735</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645593</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881977</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949745064</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,22 +7405,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L41" t="n">
-        <v>991.9887866314309</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M41" t="n">
-        <v>1634.498786631431</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N41" t="n">
-        <v>2238.277892278425</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O41" t="n">
-        <v>2399.40799366138</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7438,16 +7438,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>686.2820590119658</v>
+        <v>992.2829698086711</v>
       </c>
       <c r="C42" t="n">
-        <v>645.7770969457847</v>
+        <v>951.77800774249</v>
       </c>
       <c r="D42" t="n">
-        <v>618.5673122006306</v>
+        <v>924.5682229973359</v>
       </c>
       <c r="E42" t="n">
-        <v>596.6763049057694</v>
+        <v>727.3319471348246</v>
       </c>
       <c r="F42" t="n">
-        <v>577.8518176957928</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G42" t="n">
-        <v>573.8118062344539</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H42" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>1658.367018159816</v>
+        <v>1737.789794027844</v>
       </c>
       <c r="S42" t="n">
-        <v>1298.637139413254</v>
+        <v>1604.638050209959</v>
       </c>
       <c r="T42" t="n">
-        <v>1216.439816056512</v>
+        <v>1522.440726853217</v>
       </c>
       <c r="U42" t="n">
-        <v>1136.478522607115</v>
+        <v>1442.47943340382</v>
       </c>
       <c r="V42" t="n">
-        <v>1042.023303221741</v>
+        <v>1348.024214018446</v>
       </c>
       <c r="W42" t="n">
-        <v>929.5251790703986</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X42" t="n">
-        <v>829.6638260952597</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y42" t="n">
-        <v>750.4806010789623</v>
+        <v>1056.481511875668</v>
       </c>
     </row>
     <row r="43">
@@ -7536,55 +7536,55 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>686.6440969024735</v>
+        <v>686.6440969023969</v>
       </c>
       <c r="C43" t="n">
-        <v>734.4361027209093</v>
+        <v>734.4361027208327</v>
       </c>
       <c r="D43" t="n">
-        <v>769.5452468459093</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E43" t="n">
-        <v>809.1641510573223</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F43" t="n">
-        <v>855.3151236492578</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G43" t="n">
-        <v>931.125814126307</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H43" t="n">
-        <v>1027.892525187344</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I43" t="n">
-        <v>1189.283805434902</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J43" t="n">
-        <v>1515.576154611944</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K43" t="n">
-        <v>1619.080700024222</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L43" t="n">
-        <v>1608.654647405833</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468665</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605563</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111774</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.929907664598</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425882363</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949748929</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7596,16 +7596,16 @@
         <v>332.7843563872555</v>
       </c>
       <c r="V43" t="n">
-        <v>453.3957492732781</v>
+        <v>453.3957492732014</v>
       </c>
       <c r="W43" t="n">
-        <v>547.0766675329555</v>
+        <v>547.0766675328789</v>
       </c>
       <c r="X43" t="n">
-        <v>619.8974585571491</v>
+        <v>619.8974585570725</v>
       </c>
       <c r="Y43" t="n">
-        <v>653.0967592361814</v>
+        <v>653.0967592361047</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H44" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
@@ -7642,49 +7642,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>523.631587033441</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M44" t="n">
-        <v>1166.141587033441</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N44" t="n">
-        <v>1170.453074689115</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>588.6177696982188</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C45" t="n">
-        <v>548.1128076320377</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D45" t="n">
-        <v>520.9030228868836</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E45" t="n">
-        <v>499.0120155920224</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F45" t="n">
-        <v>480.1875283820457</v>
+        <v>235.3678800076487</v>
       </c>
       <c r="G45" t="n">
-        <v>476.1475169207069</v>
+        <v>231.3278685463099</v>
       </c>
       <c r="H45" t="n">
-        <v>147.842492699622</v>
+        <v>227.2652685676493</v>
       </c>
       <c r="I45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U45" t="n">
-        <v>1363.056657535792</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1156.103313999076</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1056.241961023937</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
-        <v>977.0587360076396</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="46">
@@ -7779,49 +7779,49 @@
         <v>734.4361027208327</v>
       </c>
       <c r="D46" t="n">
-        <v>769.5452468459202</v>
+        <v>769.5452468458327</v>
       </c>
       <c r="E46" t="n">
-        <v>809.1641510573332</v>
+        <v>809.1641510572457</v>
       </c>
       <c r="F46" t="n">
-        <v>855.3151236492687</v>
+        <v>855.3151236491811</v>
       </c>
       <c r="G46" t="n">
-        <v>931.1258141263179</v>
+        <v>931.1258141262304</v>
       </c>
       <c r="H46" t="n">
-        <v>1027.892525187355</v>
+        <v>1027.892525187267</v>
       </c>
       <c r="I46" t="n">
-        <v>1189.283805434913</v>
+        <v>1189.283805434826</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611955</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.080700024233</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405844</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468676</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605573</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111784</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.929907664609</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425882474</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949750032</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7967,22 +7967,22 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>502.5418702571336</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>183.5817792952637</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>639.5838718235262</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,22 +8444,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>472.2608914614128</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>404.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="Q8" t="n">
-        <v>311.8831458198699</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L11" t="n">
-        <v>430.7657085427137</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>579.9613438924174</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,25 +8915,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L14" t="n">
-        <v>258.8704074657004</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>301.434429149855</v>
+        <v>481.0075770556116</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,16 +9149,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.0880804020101</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L17" t="n">
-        <v>17.50927946942295</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>950.4344291498551</v>
+        <v>537.6389720331213</v>
       </c>
       <c r="N17" t="n">
         <v>230.4920535472222</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>26.68372459829277</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>248.0013330166451</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>27.14469655484982</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,16 +9860,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>179.1121759491998</v>
       </c>
       <c r="K26" t="n">
         <v>473.0880804020101</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M26" t="n">
-        <v>911.3123136417682</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N26" t="n">
         <v>879.4920535472222</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,13 +10106,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>950.4344291498551</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N29" t="n">
-        <v>234.8470915832563</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -10340,7 +10340,7 @@
         <v>473.08808040201</v>
       </c>
       <c r="L32" t="n">
-        <v>430.7657085427136</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M32" t="n">
         <v>301.434429149855</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>421.2909076101267</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,16 +10574,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
-        <v>537.1780000765643</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,13 +10814,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427137</v>
       </c>
       <c r="M38" t="n">
-        <v>361.7270524351312</v>
+        <v>579.9613438924174</v>
       </c>
       <c r="N38" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M41" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>840.3699380391354</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11294,16 +11294,16 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>234.8470915832563</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O44" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23423,7 +23423,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8382458495973992</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8382458495961096</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23660,7 +23660,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495925071</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -25076,7 +25076,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495663947</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.838245849559641</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25793,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.8382458495973992</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495213747</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495104537</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26302,16 +26302,16 @@
         <v>1385292.614675425</v>
       </c>
       <c r="M2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675425</v>
       </c>
       <c r="N2" t="n">
-        <v>1385292.614675426</v>
+        <v>1385292.614675425</v>
       </c>
       <c r="O2" t="n">
-        <v>1385292.614675427</v>
+        <v>1385292.614675425</v>
       </c>
       <c r="P2" t="n">
-        <v>1385292.614675428</v>
+        <v>1385292.614675425</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667653</v>
+        <v>570963.5697337884</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259448</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216768</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497197</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.223658956</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604943</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.493408911</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518161.4096990889</v>
+        <v>524662.7746320656</v>
       </c>
       <c r="C6" t="n">
-        <v>751268.3318865778</v>
+        <v>757769.6968195547</v>
       </c>
       <c r="D6" t="n">
-        <v>753279.9793024015</v>
+        <v>759781.3442353787</v>
       </c>
       <c r="E6" t="n">
-        <v>231859.0858792503</v>
+        <v>238322.0770096043</v>
       </c>
       <c r="F6" t="n">
-        <v>823095.1486974731</v>
+        <v>829558.1398278271</v>
       </c>
       <c r="G6" t="n">
-        <v>824783.5382191261</v>
+        <v>831246.5293494804</v>
       </c>
       <c r="H6" t="n">
-        <v>826474.2711290884</v>
+        <v>832937.2622594432</v>
       </c>
       <c r="I6" t="n">
-        <v>828167.3643296364</v>
+        <v>834630.355459991</v>
       </c>
       <c r="J6" t="n">
-        <v>441414.8349445605</v>
+        <v>447877.8260749152</v>
       </c>
       <c r="K6" t="n">
-        <v>831560.7003233945</v>
+        <v>838023.6914537487</v>
       </c>
       <c r="L6" t="n">
-        <v>833260.978045738</v>
+        <v>839723.9691760924</v>
       </c>
       <c r="M6" t="n">
-        <v>738163.6859257062</v>
+        <v>744626.6770560603</v>
       </c>
       <c r="N6" t="n">
-        <v>836668.8420164699</v>
+        <v>843131.8331468242</v>
       </c>
       <c r="O6" t="n">
-        <v>581576.4646149323</v>
+        <v>588039.4557452858</v>
       </c>
       <c r="P6" t="n">
-        <v>840086.572266517</v>
+        <v>846549.5633968696</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27515,10 +27515,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27533,7 +27533,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,19 +27557,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>92.30037099958383</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>30.47344446279683</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>279.9949965083621</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>353.251828380033</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>124.0957664680556</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K4" t="n">
         <v>267.1509377355693</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>245.1326461704237</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>58.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>246.3012605100723</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27843,22 +27843,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>171.1020457840527</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>344.316610334412</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27888,16 +27888,16 @@
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>395.5044738419193</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
         <v>134.2726973711268</v>
@@ -27958,7 +27958,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,10 +28040,10 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>78.01946960411124</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>280.8836272603908</v>
       </c>
       <c r="V9" t="n">
         <v>40.51066719152016</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28080,22 +28080,22 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>376.5799194282311</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>359.011030646429</v>
       </c>
       <c r="U10" t="n">
         <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28162,10 +28162,10 @@
         <v>321</v>
       </c>
       <c r="H11" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
@@ -28232,10 +28232,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28277,19 +28277,19 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>321</v>
+        <v>321.0000000000012</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28393,7 +28393,7 @@
         <v>321</v>
       </c>
       <c r="F14" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G14" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28460,16 +28460,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>321</v>
@@ -28481,7 +28481,7 @@
         <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>191.6509141932353</v>
+        <v>18.05909831126235</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28514,19 +28514,19 @@
         <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>321</v>
@@ -28630,7 +28630,7 @@
         <v>321</v>
       </c>
       <c r="F17" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G17" t="n">
         <v>321</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -28715,10 +28715,10 @@
         <v>321</v>
       </c>
       <c r="H18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28742,10 +28742,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>96.68764642060938</v>
       </c>
       <c r="S18" t="n">
         <v>321</v>
@@ -28867,7 +28867,7 @@
         <v>321</v>
       </c>
       <c r="F20" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G20" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28937,22 +28937,22 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -28991,7 +28991,7 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
         <v>321</v>
@@ -29003,7 +29003,7 @@
         <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29067,7 +29067,7 @@
         <v>321</v>
       </c>
       <c r="T22" t="n">
-        <v>321</v>
+        <v>321.0000000000048</v>
       </c>
       <c r="U22" t="n">
         <v>321</v>
@@ -29104,7 +29104,7 @@
         <v>321</v>
       </c>
       <c r="F23" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="G23" t="n">
         <v>321</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,16 +29174,16 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,19 +29228,19 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
         <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29420,7 +29420,7 @@
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
@@ -29453,31 +29453,31 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U27" t="n">
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29632,7 +29632,7 @@
         <v>321</v>
       </c>
       <c r="X29" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="Y29" t="n">
         <v>321</v>
@@ -29651,13 +29651,13 @@
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
         <v>321</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29705,16 +29705,16 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>226.036732227374</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
     </row>
     <row r="31">
@@ -29815,7 +29815,7 @@
         <v>321</v>
       </c>
       <c r="F32" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G32" t="n">
         <v>321</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29885,7 +29885,7 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29900,7 +29900,7 @@
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>226.0367322273742</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="I33" t="n">
         <v>191.6509141932353</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29945,7 +29945,7 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -30128,7 +30128,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30137,7 +30137,7 @@
         <v>321</v>
       </c>
       <c r="H36" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="I36" t="n">
         <v>191.6509141932353</v>
@@ -30164,13 +30164,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
       </c>
       <c r="S36" t="n">
-        <v>226.036732227374</v>
+        <v>321</v>
       </c>
       <c r="T36" t="n">
         <v>321</v>
@@ -30179,7 +30179,7 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W36" t="n">
         <v>321</v>
@@ -30264,7 +30264,7 @@
         <v>321</v>
       </c>
       <c r="X37" t="n">
-        <v>321.0000000000314</v>
+        <v>321</v>
       </c>
       <c r="Y37" t="n">
         <v>321</v>
@@ -30359,7 +30359,7 @@
         <v>321</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D39" t="n">
         <v>321</v>
@@ -30371,13 +30371,13 @@
         <v>321</v>
       </c>
       <c r="G39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
         <v>321</v>
@@ -30413,7 +30413,7 @@
         <v>321</v>
       </c>
       <c r="U39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V39" t="n">
         <v>321</v>
@@ -30422,10 +30422,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>96.68764642060955</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30459,7 +30459,7 @@
         <v>321</v>
       </c>
       <c r="J40" t="n">
-        <v>321.0000000000387</v>
+        <v>321</v>
       </c>
       <c r="K40" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346856</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30602,19 +30602,19 @@
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>147.4081841180265</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>96.6876464206095</v>
+        <v>321</v>
       </c>
       <c r="T42" t="n">
         <v>321</v>
@@ -30732,7 +30732,7 @@
         <v>321</v>
       </c>
       <c r="V43" t="n">
-        <v>321.0000000000775</v>
+        <v>321</v>
       </c>
       <c r="W43" t="n">
         <v>321</v>
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,28 +30830,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
-        <v>96.68764642060954</v>
+        <v>18.05909831126257</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30887,7 +30887,7 @@
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V45" t="n">
         <v>321</v>
@@ -30915,7 +30915,7 @@
         <v>321</v>
       </c>
       <c r="D46" t="n">
-        <v>321.0000000000884</v>
+        <v>321</v>
       </c>
       <c r="E46" t="n">
         <v>321</v>
@@ -34746,22 +34746,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>248.0502805878618</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>294.1798838637633</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
         <v>374</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>80.52658173198827</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
@@ -34901,7 +34901,7 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>101.830981566574</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="K5" t="n">
-        <v>373.9999999999999</v>
+        <v>52.15992964824122</v>
       </c>
       <c r="L5" t="n">
         <v>64.70900502512563</v>
@@ -34992,7 +34992,7 @@
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35001,7 +35001,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35129,22 +35129,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>77.16567259884262</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35174,16 +35174,16 @@
         <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>196.3341636257031</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,22 +35223,22 @@
         <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>306.7289592406478</v>
+      </c>
+      <c r="Q8" t="n">
         <v>374</v>
-      </c>
-      <c r="N8" t="n">
-        <v>374</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>58.67867865278593</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>183.3412755627363</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35366,22 +35366,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>131.7199810129305</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>149.7723657795156</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L11" t="n">
-        <v>649.0000000000001</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M11" t="n">
-        <v>278.5269147425624</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35475,7 +35475,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35606,13 +35606,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J13" t="n">
-        <v>329.5882314919611</v>
+        <v>329.5882314919623</v>
       </c>
       <c r="K13" t="n">
         <v>104.5500458709881</v>
@@ -35694,25 +35694,25 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>477.1046989229868</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>179.5731479057567</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35928,16 +35928,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>649</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>235.7435709267094</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>236.2045428832663</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
-        <v>175.9119195979899</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.200256351209361</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>113.625925297021</v>
+        <v>113.6259252970258</v>
       </c>
       <c r="U22" t="n">
         <v>170.0754447911158</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L23" t="n">
         <v>218.2342914572864</v>
@@ -36414,7 +36414,7 @@
         <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36423,7 +36423,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
-        <v>592.3686050224903</v>
+        <v>3.661228307766413</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36639,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>82.3301394835529</v>
+        <v>261.4423154327527</v>
       </c>
       <c r="K26" t="n">
         <v>649</v>
       </c>
       <c r="L26" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>609.8778844919133</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>649</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
         <v>175.9119195979899</v>
@@ -36885,13 +36885,13 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
+        <v>60.29262328527617</v>
+      </c>
+      <c r="N29" t="n">
         <v>649</v>
       </c>
-      <c r="N29" t="n">
-        <v>4.355038036034114</v>
-      </c>
       <c r="O29" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
         <v>198.5777841804241</v>
@@ -37119,7 +37119,7 @@
         <v>648.9999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>649</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>397.8074393630433</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L35" t="n">
         <v>649</v>
       </c>
       <c r="M35" t="n">
-        <v>235.7435709267093</v>
+        <v>649</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37371,7 +37371,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
-        <v>592.3686050224903</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37550,7 +37550,7 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X37" t="n">
-        <v>73.5563545699239</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y37" t="n">
         <v>33.53464715053764</v>
@@ -37593,13 +37593,13 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>60.29262328527617</v>
+        <v>278.5269147425624</v>
       </c>
       <c r="N38" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37739,13 +37739,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J40" t="n">
-        <v>329.5882314919998</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K40" t="n">
         <v>104.5500458709881</v>
@@ -37827,16 +37827,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L41" t="n">
         <v>649</v>
-      </c>
-      <c r="L41" t="n">
-        <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38018,7 +38018,7 @@
         <v>170.0754447911158</v>
       </c>
       <c r="V43" t="n">
-        <v>121.8296897838613</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W43" t="n">
         <v>94.62719016129032</v>
@@ -38064,7 +38064,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
         <v>218.2342914572864</v>
@@ -38073,16 +38073,16 @@
         <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>4.355038036034114</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O44" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38201,7 +38201,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>35.4637819445329</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E46" t="n">
         <v>40.01909516304346</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
